--- a/xls/square_16_tri3_7.xlsx
+++ b/xls/square_16_tri3_7.xlsx
@@ -482,13 +482,13 @@
         <v>294</v>
       </c>
       <c r="I7">
-        <v>3.0228657462210706</v>
+        <v>3.0228641854328795</v>
       </c>
       <c r="J7">
-        <v>0.014926237361620595</v>
+        <v>0.014916538880141625</v>
       </c>
       <c r="K7">
-        <v>0.08825405809283822</v>
+        <v>0.08825220848519054</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -517,13 +517,13 @@
         <v>384</v>
       </c>
       <c r="I8">
-        <v>-1.5990147104868981</v>
+        <v>-1.5990144712677212</v>
       </c>
       <c r="J8">
-        <v>-1.42719925516059</v>
+        <v>-1.4271994961218677</v>
       </c>
       <c r="K8">
-        <v>-0.9305835624631009</v>
+        <v>-0.930583652157572</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -552,13 +552,13 @@
         <v>486</v>
       </c>
       <c r="I9">
-        <v>-1.6229581112448719</v>
+        <v>-1.6229580700632524</v>
       </c>
       <c r="J9">
-        <v>-1.4663837961655188</v>
+        <v>-1.4663838301420409</v>
       </c>
       <c r="K9">
-        <v>-0.7587165655506363</v>
+        <v>-0.7587164781054475</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -587,13 +587,13 @@
         <v>600</v>
       </c>
       <c r="I10">
-        <v>-1.53411473476077</v>
+        <v>-1.5341146139939421</v>
       </c>
       <c r="J10">
-        <v>-1.220106081193808</v>
+        <v>-1.2201060288001817</v>
       </c>
       <c r="K10">
-        <v>-0.4214616787583749</v>
+        <v>-0.4214616777408106</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -622,13 +622,13 @@
         <v>726</v>
       </c>
       <c r="I11">
-        <v>-1.120858827637471</v>
+        <v>-1.1208589009448833</v>
       </c>
       <c r="J11">
-        <v>-0.8436716552771965</v>
+        <v>-0.8436717076058301</v>
       </c>
       <c r="K11">
-        <v>-0.03048202707497034</v>
+        <v>-0.030482009130394994</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -657,13 +657,13 @@
         <v>864</v>
       </c>
       <c r="I12">
-        <v>-1.4784314605226911</v>
+        <v>-1.478431469300021</v>
       </c>
       <c r="J12">
-        <v>-1.254304738413784</v>
+        <v>-1.2543046858339766</v>
       </c>
       <c r="K12">
-        <v>-0.39482995575289404</v>
+        <v>-0.39483005238069263</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -692,13 +692,13 @@
         <v>1014</v>
       </c>
       <c r="I13">
-        <v>-0.6044365498434262</v>
+        <v>-0.6044365688049422</v>
       </c>
       <c r="J13">
-        <v>-0.5762275226526372</v>
+        <v>-0.5762275285355364</v>
       </c>
       <c r="K13">
-        <v>0.2602315737226326</v>
+        <v>0.2602315782712359</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -727,13 +727,13 @@
         <v>1176</v>
       </c>
       <c r="I14">
-        <v>-0.7256819378744244</v>
+        <v>-0.7256819255430051</v>
       </c>
       <c r="J14">
-        <v>-0.6960209743940062</v>
+        <v>-0.6960209816095341</v>
       </c>
       <c r="K14">
-        <v>0.25898087542755654</v>
+        <v>0.258980873176032</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -762,13 +762,13 @@
         <v>1350</v>
       </c>
       <c r="I15">
-        <v>-0.36390759138522494</v>
+        <v>-0.3639075862851588</v>
       </c>
       <c r="J15">
-        <v>-0.3629505538370545</v>
+        <v>-0.36295054823629824</v>
       </c>
       <c r="K15">
-        <v>0.4424483176676621</v>
+        <v>0.4424483169075825</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -797,13 +797,13 @@
         <v>1536</v>
       </c>
       <c r="I16">
-        <v>-0.5202894416906533</v>
+        <v>-0.5202894287689994</v>
       </c>
       <c r="J16">
-        <v>-0.5114484482378251</v>
+        <v>-0.5114484367055973</v>
       </c>
       <c r="K16">
-        <v>0.26125820404381883</v>
+        <v>0.2612582021629861</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -832,13 +832,13 @@
         <v>1734</v>
       </c>
       <c r="I17">
-        <v>0.0030775783666967377</v>
+        <v>0.0030775783807430487</v>
       </c>
       <c r="J17">
-        <v>-0.0012265478069186822</v>
+        <v>-0.0012265478974558032</v>
       </c>
       <c r="K17">
-        <v>3.0242110067056553</v>
+        <v>3.024211005674443</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -867,13 +867,13 @@
         <v>1944</v>
       </c>
       <c r="I18">
-        <v>-0.0002284876768701522</v>
+        <v>-0.00022848767677998837</v>
       </c>
       <c r="J18">
-        <v>-0.00017080406966325388</v>
+        <v>-0.00017080406960127146</v>
       </c>
       <c r="K18">
-        <v>2.4205327492621573</v>
+        <v>2.420532749058417</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -902,13 +902,13 @@
         <v>2166</v>
       </c>
       <c r="I19">
-        <v>-6.402947903478746e-5</v>
+        <v>-6.402947903092958e-5</v>
       </c>
       <c r="J19">
-        <v>-4.2819803759963884e-5</v>
+        <v>-4.2819803757890374e-5</v>
       </c>
       <c r="K19">
-        <v>2.0953519300752257</v>
+        <v>2.0953519299016725</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -937,13 +937,13 @@
         <v>2400</v>
       </c>
       <c r="I20">
-        <v>-4.111292415712136e-6</v>
+        <v>-4.111292415181751e-6</v>
       </c>
       <c r="J20">
-        <v>-4.9804470840774424e-6</v>
+        <v>-4.9804470837399235e-6</v>
       </c>
       <c r="K20">
-        <v>1.843265783571319</v>
+        <v>1.8432657835631425</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -972,13 +972,13 @@
         <v>2646</v>
       </c>
       <c r="I21">
-        <v>1.2838817769799178e-5</v>
+        <v>1.2838817769992038e-5</v>
       </c>
       <c r="J21">
         <v>3.988140691388096e-6</v>
       </c>
       <c r="K21">
-        <v>1.8152504551677424</v>
+        <v>1.8152504552151179</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -1007,13 +1007,13 @@
         <v>2904</v>
       </c>
       <c r="I22">
-        <v>1.0922443278604488e-5</v>
+        <v>1.0922443279761652e-5</v>
       </c>
       <c r="J22">
-        <v>4.352273555357016e-6</v>
+        <v>4.352273555549879e-6</v>
       </c>
       <c r="K22">
-        <v>1.6577944466733292</v>
+        <v>1.657794446932337</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -1042,13 +1042,13 @@
         <v>3174</v>
       </c>
       <c r="I23">
-        <v>2.0613890449034173e-6</v>
+        <v>2.0613890447105526e-6</v>
       </c>
       <c r="J23">
-        <v>8.479403026245812e-7</v>
+        <v>8.479403024317161e-7</v>
       </c>
       <c r="K23">
-        <v>1.2701257632519292</v>
+        <v>1.2701257634876288</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -1080,10 +1080,10 @@
         <v>-5.444422023243713e-7</v>
       </c>
       <c r="J24">
-        <v>-3.7770338034863705e-7</v>
+        <v>-3.777033805897191e-7</v>
       </c>
       <c r="K24">
-        <v>1.118103919768513</v>
+        <v>1.1181039195761506</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -1112,13 +1112,13 @@
         <v>3750</v>
       </c>
       <c r="I25">
-        <v>-3.03861963546274e-7</v>
+        <v>-3.038619634498412e-7</v>
       </c>
       <c r="J25">
-        <v>-2.4332570128690654e-7</v>
+        <v>-2.4332570104582455e-7</v>
       </c>
       <c r="K25">
-        <v>1.0858225573206464</v>
+        <v>1.0858225571978162</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -1147,13 +1147,13 @@
         <v>4056</v>
       </c>
       <c r="I26">
-        <v>-3.19833104075287e-7</v>
+        <v>-3.1983310388242135e-7</v>
       </c>
       <c r="J26">
         <v>-2.480111786175715e-7</v>
       </c>
       <c r="K26">
-        <v>1.0767388597839112</v>
+        <v>1.0767388598252268</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -1182,13 +1182,13 @@
         <v>4374</v>
       </c>
       <c r="I27">
-        <v>-4.795604065608904e-7</v>
+        <v>-4.795604066573232e-7</v>
       </c>
       <c r="J27">
-        <v>-3.3280370778630414e-7</v>
+        <v>-3.328037075934385e-7</v>
       </c>
       <c r="K27">
-        <v>1.0883217584249856</v>
+        <v>1.0883217586271148</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -1217,13 +1217,13 @@
         <v>4704</v>
       </c>
       <c r="I28">
-        <v>-3.6049258998977795e-7</v>
+        <v>-3.604925898933451e-7</v>
       </c>
       <c r="J28">
         <v>-2.786667414723875e-7</v>
       </c>
       <c r="K28">
-        <v>1.1043324342895133</v>
+        <v>1.1043324343490353</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -1252,13 +1252,13 @@
         <v>5046</v>
       </c>
       <c r="I29">
-        <v>-2.397048469860242e-7</v>
+        <v>-2.397048468895914e-7</v>
       </c>
       <c r="J29">
-        <v>-2.075452231639564e-7</v>
+        <v>-2.0754522311574e-7</v>
       </c>
       <c r="K29">
-        <v>1.0824436961108097</v>
+        <v>1.0824436961405104</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -1287,13 +1287,13 @@
         <v>5400</v>
       </c>
       <c r="I30">
-        <v>-2.85067749082084e-7</v>
+        <v>-2.8506774898565114e-7</v>
       </c>
       <c r="J30">
-        <v>-2.2951154890180368e-7</v>
+        <v>-2.2951154904645288e-7</v>
       </c>
       <c r="K30">
-        <v>1.0768149638559603</v>
+        <v>1.0768149639295224</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -1322,13 +1322,13 @@
         <v>5766</v>
       </c>
       <c r="I31">
-        <v>-4.2946112149084297e-7</v>
+        <v>-4.2946112163549226e-7</v>
       </c>
       <c r="J31">
         <v>-3.018453411107356e-7</v>
       </c>
       <c r="K31">
-        <v>1.0732340518774441</v>
+        <v>1.073234052034285</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -1357,13 +1357,13 @@
         <v>6144</v>
       </c>
       <c r="I32">
-        <v>-3.3424954874151384e-7</v>
+        <v>-3.3424954878973024e-7</v>
       </c>
       <c r="J32">
-        <v>-2.49397952608102e-7</v>
+        <v>-2.4939795280096757e-7</v>
       </c>
       <c r="K32">
-        <v>1.062255974349407</v>
+        <v>1.0622559741415019</v>
       </c>
     </row>
   </sheetData>
